--- a/artfynd/A 21314-2024 artfynd.xlsx
+++ b/artfynd/A 21314-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117968458</v>
       </c>
       <c r="B2" t="n">
-        <v>97873</v>
+        <v>97875</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
